--- a/merge/ValueSet-bc-contact-point-system-value-set.xlsx
+++ b/merge/ValueSet-bc-contact-point-system-value-set.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T00:47:30+00:00</t>
+    <t>2026-03-25T21:32:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
